--- a/artfynd/S 2932-2024 artfynd.xlsx
+++ b/artfynd/S 2932-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ162"/>
+  <dimension ref="A1:AZ163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16545,10 +16545,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>132651080</v>
+        <v>136813846</v>
       </c>
       <c r="B139" t="n">
-        <v>101325</v>
+        <v>111358</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16556,16 +16556,16 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>222783</v>
+        <v>221037</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Gulsippa</t>
+          <t>Vildkaprifol</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Anemone ranunculoides</t>
+          <t>Lonicera periclymenum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -16573,32 +16573,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Skogskanten, Hammaren, Skogsmatningen, Srm</t>
+          <t>Hammargärdet, Srm</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>626789</v>
+        <v>626462</v>
       </c>
       <c r="R139" t="n">
-        <v>6571787</v>
+        <v>6571720</v>
       </c>
       <c r="S139" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -16622,22 +16610,12 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="Z139" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="AB139" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16646,72 +16624,83 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Helene Lindahl</t>
+          <t>Björn Carlsson</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Helene Lindahl</t>
+          <t>Björn Carlsson</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132651080</t>
+          <t>https://artportalen.se/Sighting/136813846</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>5735537</v>
+        <v>132651080</v>
       </c>
       <c r="B140" t="n">
-        <v>103403</v>
+        <v>101325</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>223246</v>
+        <v>222783</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Gulsippa</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Anemone ranunculoides</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Huds.</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Mariehov 200 m nv, Srm</t>
+          <t>Skogskanten, Hammaren, Skogsmatningen, Srm</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>627685</v>
+        <v>626789</v>
       </c>
       <c r="R140" t="n">
-        <v>6571948</v>
+        <v>6571787</v>
       </c>
       <c r="S140" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -16730,17 +16719,27 @@
       </c>
       <c r="W140" t="inlineStr">
         <is>
-          <t>Kärnbo</t>
+          <t>Mariefred</t>
         </is>
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2005-12-02</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2005-12-02</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16749,76 +16748,72 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
-      </c>
-      <c r="AI140" t="inlineStr">
-        <is>
-          <t>Gammelekar</t>
-        </is>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Helene Lindahl</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Helene Lindahl</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/5735537</t>
+          <t>https://artportalen.se/Sighting/132651080</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>124500</v>
+        <v>5735537</v>
       </c>
       <c r="B141" t="n">
-        <v>83304</v>
+        <v>103403</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>311</v>
+        <v>223246</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Brun nållav</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Chaenotheca phaeocephala</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Turner) Th.Fr.</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Kärnbo, Mariefred SV om Ekhov, Srm</t>
+          <t>Mariehov 200 m nv, Srm</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>627546</v>
+        <v>627685</v>
       </c>
       <c r="R141" t="n">
-        <v>6571382</v>
+        <v>6571948</v>
       </c>
       <c r="S141" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -16837,22 +16832,17 @@
       </c>
       <c r="W141" t="inlineStr">
         <is>
-          <t>Mariefred</t>
+          <t>Kärnbo</t>
         </is>
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>1994-05-08</t>
+          <t>2005-12-02</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>1994-05-08</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>ca 2,5-3 m grova ekar</t>
+          <t>2005-12-02</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16866,38 +16856,33 @@
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>ekskog</t>
-        </is>
-      </c>
-      <c r="AO141" t="inlineStr">
-        <is>
-          <t>ekbark</t>
+          <t>Gammelekar</t>
         </is>
       </c>
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124500</t>
+          <t>https://artportalen.se/Sighting/5735537</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>2218048</v>
+        <v>124500</v>
       </c>
       <c r="B142" t="n">
-        <v>78728</v>
+        <v>83304</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16905,21 +16890,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6436</v>
+        <v>311</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Gulpudrad spiklav</t>
+          <t>Brun nållav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Calicium adspersum</t>
+          <t>Chaenotheca phaeocephala</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>(Turner) Th.Fr.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -17005,62 +16990,54 @@
       <c r="AY142" t="inlineStr"/>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2218048</t>
+          <t>https://artportalen.se/Sighting/124500</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>133454863</v>
+        <v>2218048</v>
       </c>
       <c r="B143" t="n">
-        <v>56865</v>
+        <v>78728</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>100053</v>
+        <v>6436</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Gulpudrad spiklav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Erinaceus europaeus</t>
+          <t>Calicium adspersum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr"/>
-      <c r="N143" t="inlineStr"/>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Jakob Ulfssons väg 4A, Fågelsången, Srm</t>
+          <t>Kärnbo, Mariefred SV om Ekhov, Srm</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>627467</v>
+        <v>627546</v>
       </c>
       <c r="R143" t="n">
-        <v>6571440</v>
+        <v>6571382</v>
       </c>
       <c r="S143" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -17084,27 +17061,17 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>21:30</t>
+          <t>1994-05-08</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>21:30</t>
+          <t>1994-05-08</t>
         </is>
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>Igelkott stor och 2 mindre verkar leva på grösmattan och bland buskarna vid hyresrätter på Jakob Ulfssons väg 4a-6c i Mariefred. Setts av flera boenden kvällstid i ca 3 v.</t>
+          <t>ca 2,5-3 m grova ekar</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -17115,85 +17082,87 @@
       </c>
       <c r="AG143" t="b">
         <v>0</v>
+      </c>
+      <c r="AI143" t="inlineStr">
+        <is>
+          <t>ekskog</t>
+        </is>
+      </c>
+      <c r="AO143" t="inlineStr">
+        <is>
+          <t>ekbark</t>
+        </is>
       </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Ditte  Waldton</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Ditte  Waldton</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133454863</t>
+          <t>https://artportalen.se/Sighting/2218048</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>97693684</v>
+        <v>133454863</v>
       </c>
       <c r="B144" t="n">
-        <v>57899</v>
+        <v>56865</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100067</v>
+        <v>100053</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Erinaceus europaeus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr"/>
       <c r="L144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M144" t="inlineStr"/>
       <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Fågelsången, Srm</t>
+          <t>Jakob Ulfssons väg 4A, Fågelsången, Srm</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>627575</v>
+        <v>627467</v>
       </c>
       <c r="R144" t="n">
-        <v>6571371</v>
+        <v>6571440</v>
       </c>
       <c r="S144" t="n">
-        <v>125</v>
+        <v>1</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -17217,22 +17186,27 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2021-12-25</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2021-12-25</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>Igelkott stor och 2 mindre verkar leva på grösmattan och bland buskarna vid hyresrätter på Jakob Ulfssons väg 4a-6c i Mariefred. Setts av flera boenden kvällstid i ca 3 v.</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -17247,27 +17221,27 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Maria  Barkell</t>
+          <t>Ditte  Waldton</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Maria  Barkell, Daniel Brehmer</t>
+          <t>Ditte  Waldton</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97693684</t>
+          <t>https://artportalen.se/Sighting/133454863</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>97928276</v>
+        <v>97693684</v>
       </c>
       <c r="B145" t="n">
-        <v>58592</v>
+        <v>57899</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17275,16 +17249,16 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>102125</v>
+        <v>100067</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -17297,7 +17271,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" t="inlineStr">
         <is>
@@ -17341,12 +17319,22 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2022-01-05</t>
+          <t>2021-12-25</t>
+        </is>
+      </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2022-01-05</t>
+          <t>2021-12-25</t>
+        </is>
+      </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -17361,44 +17349,44 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Janne Wahlström</t>
+          <t>Maria  Barkell</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Janne Wahlström, Gittan Wahlström</t>
+          <t>Maria  Barkell, Daniel Brehmer</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97928276</t>
+          <t>https://artportalen.se/Sighting/97693684</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>101008353</v>
+        <v>97928276</v>
       </c>
       <c r="B146" t="n">
-        <v>57774</v>
+        <v>58592</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>102976</v>
+        <v>102125</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -17415,7 +17403,7 @@
       <c r="L146" t="inlineStr"/>
       <c r="M146" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N146" t="inlineStr"/>
@@ -17455,22 +17443,12 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2022-05-21</t>
-        </is>
-      </c>
-      <c r="Z146" t="inlineStr">
-        <is>
-          <t>11:54</t>
+          <t>2022-01-05</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2022-05-21</t>
-        </is>
-      </c>
-      <c r="AB146" t="inlineStr">
-        <is>
-          <t>11:54</t>
+          <t>2022-01-05</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17485,49 +17463,49 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Maria  Barkell</t>
+          <t>Janne Wahlström</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Maria  Barkell</t>
+          <t>Janne Wahlström, Gittan Wahlström</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101008353</t>
+          <t>https://artportalen.se/Sighting/97928276</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>108591177</v>
+        <v>101008353</v>
       </c>
       <c r="B147" t="n">
-        <v>57947</v>
+        <v>57774</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>102977</v>
+        <v>102976</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -17539,7 +17517,7 @@
       <c r="L147" t="inlineStr"/>
       <c r="M147" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N147" t="inlineStr"/>
@@ -17579,22 +17557,22 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2023-04-30</t>
+          <t>2022-05-21</t>
         </is>
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2023-04-30</t>
+          <t>2022-05-21</t>
         </is>
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17609,31 +17587,27 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Petter Kappel</t>
+          <t>Maria  Barkell</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Petter Kappel</t>
-        </is>
-      </c>
-      <c r="AY147" t="inlineStr">
-        <is>
-          <t>Ekoskådning</t>
-        </is>
-      </c>
+          <t>Maria  Barkell</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr"/>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/108591177</t>
+          <t>https://artportalen.se/Sighting/101008353</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>101008324</v>
+        <v>108591177</v>
       </c>
       <c r="B148" t="n">
-        <v>58439</v>
+        <v>57947</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17641,37 +17615,33 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>103018</v>
+        <v>102977</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L148" t="inlineStr"/>
       <c r="M148" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N148" t="inlineStr"/>
@@ -17711,22 +17681,22 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2022-05-21</t>
+          <t>2023-04-30</t>
         </is>
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2022-05-21</t>
+          <t>2023-04-30</t>
         </is>
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17741,59 +17711,71 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Maria  Barkell</t>
+          <t>Petter Kappel</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Maria  Barkell</t>
-        </is>
-      </c>
-      <c r="AY148" t="inlineStr"/>
+          <t>Petter Kappel</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr">
+        <is>
+          <t>Ekoskådning</t>
+        </is>
+      </c>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101008324</t>
+          <t>https://artportalen.se/Sighting/108591177</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>99396056</v>
+        <v>101008324</v>
       </c>
       <c r="B149" t="n">
-        <v>58112</v>
+        <v>58439</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>103020</v>
+        <v>103018</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr"/>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
@@ -17831,12 +17813,22 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2022-03-22</t>
+          <t>2022-05-21</t>
+        </is>
+      </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2022-03-22</t>
+          <t>2022-05-21</t>
+        </is>
+      </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17851,59 +17843,59 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Britt-Marie Sohlström</t>
+          <t>Maria  Barkell</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Britt-Marie Sohlström, Roine Johansson</t>
+          <t>Maria  Barkell</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/99396056</t>
+          <t>https://artportalen.se/Sighting/101008324</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>101145945</v>
+        <v>99396056</v>
       </c>
       <c r="B150" t="n">
-        <v>58353</v>
+        <v>58112</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>103037</v>
+        <v>103020</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K150" t="inlineStr"/>
       <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>föda åt ungar</t>
-        </is>
-      </c>
+      <c r="M150" t="inlineStr"/>
       <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
@@ -17941,12 +17933,12 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2022-05-25</t>
+          <t>2022-03-22</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2022-05-25</t>
+          <t>2022-03-22</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17961,27 +17953,27 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Annika Henschen</t>
+          <t>Britt-Marie Sohlström</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Annika Henschen</t>
+          <t>Britt-Marie Sohlström, Roine Johansson</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101145945</t>
+          <t>https://artportalen.se/Sighting/99396056</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>106006049</v>
+        <v>101145945</v>
       </c>
       <c r="B151" t="n">
-        <v>58602</v>
+        <v>58353</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17989,33 +17981,29 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>103042</v>
+        <v>103037</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
       <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr"/>
       <c r="M151" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>föda åt ungar</t>
         </is>
       </c>
       <c r="N151" t="inlineStr"/>
@@ -18055,22 +18043,12 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2023-01-15</t>
-        </is>
-      </c>
-      <c r="Z151" t="inlineStr">
-        <is>
-          <t>14:40</t>
+          <t>2022-05-25</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2023-01-15</t>
-        </is>
-      </c>
-      <c r="AB151" t="inlineStr">
-        <is>
-          <t>14:40</t>
+          <t>2022-05-25</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -18085,48 +18063,44 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Petter Kappel</t>
+          <t>Annika Henschen</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Petter Kappel</t>
-        </is>
-      </c>
-      <c r="AY151" t="inlineStr">
-        <is>
-          <t>Ekoskådning</t>
-        </is>
-      </c>
+          <t>Annika Henschen</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr"/>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106006049</t>
+          <t>https://artportalen.se/Sighting/101145945</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>98383588</v>
+        <v>106006049</v>
       </c>
       <c r="B152" t="n">
-        <v>58636</v>
+        <v>58602</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>103044</v>
+        <v>103042</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -18136,7 +18110,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K152" t="inlineStr"/>
@@ -18183,22 +18157,22 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2022-01-29</t>
+          <t>2023-01-15</t>
         </is>
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2022-01-29</t>
+          <t>2023-01-15</t>
         </is>
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -18213,54 +18187,58 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Maria  Barkell</t>
+          <t>Petter Kappel</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Maria  Barkell, Elisabeth Byskata-Evjen, Ann-Marie Thorstenson</t>
-        </is>
-      </c>
-      <c r="AY152" t="inlineStr"/>
+          <t>Petter Kappel</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr">
+        <is>
+          <t>Ekoskådning</t>
+        </is>
+      </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98383588</t>
+          <t>https://artportalen.se/Sighting/106006049</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>97693693</v>
+        <v>98383588</v>
       </c>
       <c r="B153" t="n">
-        <v>58676</v>
+        <v>58636</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>103055</v>
+        <v>103044</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K153" t="inlineStr"/>
@@ -18307,22 +18285,22 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2021-12-25</t>
+          <t>2022-01-29</t>
         </is>
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2021-12-25</t>
+          <t>2022-01-29</t>
         </is>
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -18342,39 +18320,39 @@
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Maria  Barkell, Daniel Brehmer</t>
+          <t>Maria  Barkell, Elisabeth Byskata-Evjen, Ann-Marie Thorstenson</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97693693</t>
+          <t>https://artportalen.se/Sighting/98383588</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>98383581</v>
+        <v>97693693</v>
       </c>
       <c r="B154" t="n">
-        <v>58085</v>
+        <v>58676</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>205976</v>
+        <v>103055</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -18384,7 +18362,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K154" t="inlineStr"/>
@@ -18431,22 +18409,22 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2022-01-29</t>
+          <t>2021-12-25</t>
         </is>
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2022-01-29</t>
+          <t>2021-12-25</t>
         </is>
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -18466,60 +18444,72 @@
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Maria  Barkell, Elisabeth Byskata-Evjen, Ann-Marie Thorstenson</t>
+          <t>Maria  Barkell, Daniel Brehmer</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98383581</t>
+          <t>https://artportalen.se/Sighting/97693693</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128193184</v>
+        <v>98383581</v>
       </c>
       <c r="B155" t="n">
-        <v>92699</v>
+        <v>58085</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>366</v>
+        <v>205976</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Fäbodhagen, Srm</t>
+          <t>Fågelsången, Srm</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>626781</v>
+        <v>627575</v>
       </c>
       <c r="R155" t="n">
-        <v>6569734</v>
+        <v>6571371</v>
       </c>
       <c r="S155" t="n">
-        <v>10</v>
+        <v>125</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -18543,12 +18533,22 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2022-01-29</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2022-01-29</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -18563,27 +18563,27 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Birgitta Arwidsson</t>
+          <t>Maria  Barkell</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Birgitta Arwidsson</t>
+          <t>Maria  Barkell, Elisabeth Byskata-Evjen, Ann-Marie Thorstenson</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128193184</t>
+          <t>https://artportalen.se/Sighting/98383581</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>6740853</v>
+        <v>128193184</v>
       </c>
       <c r="B156" t="n">
-        <v>79795</v>
+        <v>92699</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18591,37 +18591,37 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Gul dropplav</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Cliostomum corrugatum</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.:Fr.) Fr.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>GAMMAL EK V KARLSBORG (10H4g02), Srm</t>
+          <t>Fäbodhagen, Srm</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>626728</v>
+        <v>626781</v>
       </c>
       <c r="R156" t="n">
-        <v>6569770</v>
+        <v>6569734</v>
       </c>
       <c r="S156" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -18645,17 +18645,12 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>1997-06-11</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>1997-06-11</t>
-        </is>
-      </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>100746021 / CLI CORR / Enstaka-sparsam (1)  / OBJ.AREA:0,1 ha</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -18666,45 +18661,31 @@
       </c>
       <c r="AG156" t="b">
         <v>0</v>
-      </c>
-      <c r="AI156" t="inlineStr">
-        <is>
-          <t>Grova ädellövträd /</t>
-        </is>
-      </c>
-      <c r="AO156" t="inlineStr">
-        <is>
-          <t>Gammal grov ek</t>
-        </is>
       </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Niklas Lönnell</t>
+          <t>Birgitta Arwidsson</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Rikard Sellberg</t>
-        </is>
-      </c>
-      <c r="AY156" t="inlineStr">
-        <is>
-          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
-        </is>
-      </c>
+          <t>Birgitta Arwidsson</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr"/>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6740853</t>
+          <t>https://artportalen.se/Sighting/128193184</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>96212364</v>
+        <v>6740853</v>
       </c>
       <c r="B157" t="n">
-        <v>91225</v>
+        <v>79795</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18712,48 +18693,34 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1466</v>
+        <v>374</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Knottrig rottryffel</t>
+          <t>Gul dropplav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Scleroderma verrucosum</t>
+          <t>Cliostomum corrugatum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Bull.) Pers., nom.sanct.</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Karin Månsdotterstugan, Karin Månsdotterstugan, Strängnäs, Srm</t>
+          <t>GAMMAL EK V KARLSBORG (10H4g02), Srm</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>627163</v>
+        <v>626728</v>
       </c>
       <c r="R157" t="n">
-        <v>6569694</v>
+        <v>6569770</v>
       </c>
       <c r="S157" t="n">
         <v>25</v>
@@ -18780,22 +18747,17 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2021-09-19</t>
-        </is>
-      </c>
-      <c r="Z157" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>1997-06-11</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2021-09-19</t>
-        </is>
-      </c>
-      <c r="AB157" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>1997-06-11</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>100746021 / CLI CORR / Enstaka-sparsam (1)  / OBJ.AREA:0,1 ha</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -18806,31 +18768,45 @@
       </c>
       <c r="AG157" t="b">
         <v>0</v>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>Grova ädellövträd /</t>
+        </is>
+      </c>
+      <c r="AO157" t="inlineStr">
+        <is>
+          <t>Gammal grov ek</t>
+        </is>
       </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Sanna Volny</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Sanna Volny</t>
-        </is>
-      </c>
-      <c r="AY157" t="inlineStr"/>
+          <t>Rikard Sellberg</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96212364</t>
+          <t>https://artportalen.se/Sighting/6740853</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>431055</v>
+        <v>96212364</v>
       </c>
       <c r="B158" t="n">
-        <v>83312</v>
+        <v>91225</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18838,34 +18814,48 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Knottrig rottryffel</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Scleroderma verrucosum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr"/>
+          <t>(Bull.) Pers., nom.sanct.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>GAMMAL EK V KARLSBORG (10H4g02), Srm</t>
+          <t>Karin Månsdotterstugan, Karin Månsdotterstugan, Strängnäs, Srm</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>626728</v>
+        <v>627163</v>
       </c>
       <c r="R158" t="n">
-        <v>6569770</v>
+        <v>6569694</v>
       </c>
       <c r="S158" t="n">
         <v>25</v>
@@ -18892,17 +18882,22 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>1997-06-11</t>
+          <t>2021-09-19</t>
+        </is>
+      </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>1997-06-11</t>
-        </is>
-      </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>100746021 / SCL CONI / Tämligen allmän (2)  / OBJ.AREA:0,1 ha</t>
+          <t>2021-09-19</t>
+        </is>
+      </c>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -18913,87 +18908,69 @@
       </c>
       <c r="AG158" t="b">
         <v>0</v>
-      </c>
-      <c r="AI158" t="inlineStr">
-        <is>
-          <t>Grova ädellövträd /</t>
-        </is>
-      </c>
-      <c r="AO158" t="inlineStr">
-        <is>
-          <t>Gammal grov ek</t>
-        </is>
       </c>
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Niklas Lönnell</t>
+          <t>Sanna Volny</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Rikard Sellberg</t>
-        </is>
-      </c>
-      <c r="AY158" t="inlineStr">
-        <is>
-          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
-        </is>
-      </c>
+          <t>Sanna Volny</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr"/>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/431055</t>
+          <t>https://artportalen.se/Sighting/96212364</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>120123778</v>
+        <v>431055</v>
       </c>
       <c r="B159" t="n">
-        <v>56845</v>
+        <v>83312</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100053</v>
+        <v>1467</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Erinaceus europaeus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Kajsa Rultas källa, Srm</t>
+          <t>GAMMAL EK V KARLSBORG (10H4g02), Srm</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>626979</v>
+        <v>626728</v>
       </c>
       <c r="R159" t="n">
-        <v>6569653</v>
+        <v>6569770</v>
       </c>
       <c r="S159" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -19017,22 +18994,17 @@
       </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
-        </is>
-      </c>
-      <c r="Z159" t="inlineStr">
-        <is>
-          <t>22:00</t>
+          <t>1997-06-11</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
-        </is>
-      </c>
-      <c r="AB159" t="inlineStr">
-        <is>
-          <t>22:00</t>
+          <t>1997-06-11</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>100746021 / SCL CONI / Tämligen allmän (2)  / OBJ.AREA:0,1 ha</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -19043,32 +19015,42 @@
       </c>
       <c r="AG159" t="b">
         <v>0</v>
+      </c>
+      <c r="AI159" t="inlineStr">
+        <is>
+          <t>Grova ädellövträd /</t>
+        </is>
+      </c>
+      <c r="AO159" t="inlineStr">
+        <is>
+          <t>Gammal grov ek</t>
+        </is>
       </c>
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Johan Nilsson</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Via Johan Nilsson</t>
+          <t>Rikard Sellberg</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
         <is>
-          <t>Nordens Ark - Tillsammans för Sveriges igelkottar</t>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120123778</t>
+          <t>https://artportalen.se/Sighting/431055</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>124575936</v>
+        <v>120123778</v>
       </c>
       <c r="B160" t="n">
         <v>56845</v>
@@ -19101,31 +19083,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
-      <c r="L160" t="inlineStr"/>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>gående/springande</t>
-        </is>
-      </c>
-      <c r="N160" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Karin Månsdottersstugan, Hedlandet, Srm</t>
+          <t>Kajsa Rultas källa, Srm</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>627175</v>
+        <v>626979</v>
       </c>
       <c r="R160" t="n">
-        <v>6569703</v>
+        <v>6569653</v>
       </c>
       <c r="S160" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -19149,22 +19119,22 @@
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -19179,24 +19149,28 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Moa Volny</t>
+          <t>Johan Nilsson</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Moa Volny</t>
-        </is>
-      </c>
-      <c r="AY160" t="inlineStr"/>
+          <t>Via Johan Nilsson</t>
+        </is>
+      </c>
+      <c r="AY160" t="inlineStr">
+        <is>
+          <t>Nordens Ark - Tillsammans för Sveriges igelkottar</t>
+        </is>
+      </c>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124575936</t>
+          <t>https://artportalen.se/Sighting/120123778</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>127919799</v>
+        <v>124575936</v>
       </c>
       <c r="B161" t="n">
         <v>56845</v>
@@ -19229,9 +19203,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t>adult</t>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>gående/springande</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -19241,17 +19217,17 @@
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>D 986 1, 647 92 Mariefred, Srm</t>
+          <t>Karin Månsdottersstugan, Hedlandet, Srm</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>627238</v>
+        <v>627175</v>
       </c>
       <c r="R161" t="n">
-        <v>6569523</v>
+        <v>6569703</v>
       </c>
       <c r="S161" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -19275,22 +19251,22 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -19305,53 +19281,49 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Johan Möller</t>
+          <t>Moa Volny</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Via Johan Möller</t>
-        </is>
-      </c>
-      <c r="AY161" t="inlineStr">
-        <is>
-          <t>WWF - Tillsammans för Sveriges igelkottar</t>
-        </is>
-      </c>
+          <t>Moa Volny</t>
+        </is>
+      </c>
+      <c r="AY161" t="inlineStr"/>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127919799</t>
+          <t>https://artportalen.se/Sighting/124575936</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>118850750</v>
+        <v>127919799</v>
       </c>
       <c r="B162" t="n">
-        <v>56895</v>
+        <v>56845</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>100088</v>
+        <v>100053</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Erinaceus europaeus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -19359,32 +19331,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr">
         <is>
-          <t>årsunge</t>
-        </is>
-      </c>
-      <c r="L162" t="inlineStr"/>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
-      <c r="N162" t="inlineStr"/>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Hedlandet, Hedlandet, Srm</t>
+          <t>D 986 1, 647 92 Mariefred, Srm</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>627351</v>
+        <v>627238</v>
       </c>
       <c r="R162" t="n">
-        <v>6569673</v>
+        <v>6569523</v>
       </c>
       <c r="S162" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -19408,12 +19377,22 @@
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -19422,23 +19401,146 @@
       <c r="AE162" t="b">
         <v>0</v>
       </c>
-      <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="b">
         <v>0</v>
       </c>
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
+          <t>Johan Möller</t>
+        </is>
+      </c>
+      <c r="AX162" t="inlineStr">
+        <is>
+          <t>Via Johan Möller</t>
+        </is>
+      </c>
+      <c r="AY162" t="inlineStr">
+        <is>
+          <t>WWF - Tillsammans för Sveriges igelkottar</t>
+        </is>
+      </c>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127919799</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>118850750</v>
+      </c>
+      <c r="B163" t="n">
+        <v>56895</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>100088</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Vanlig snok</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Natrix natrix</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr"/>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>Hedlandet, Hedlandet, Srm</t>
+        </is>
+      </c>
+      <c r="Q163" t="n">
+        <v>627351</v>
+      </c>
+      <c r="R163" t="n">
+        <v>6569673</v>
+      </c>
+      <c r="S163" t="n">
+        <v>25</v>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>Mariefred</t>
+        </is>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="AD163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF163" t="inlineStr"/>
+      <c r="AG163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT163" t="inlineStr"/>
+      <c r="AW163" t="inlineStr">
+        <is>
           <t>Ida Jagare</t>
         </is>
       </c>
-      <c r="AX162" t="inlineStr">
+      <c r="AX163" t="inlineStr">
         <is>
           <t>Ida Jagare</t>
         </is>
       </c>
-      <c r="AY162" t="inlineStr"/>
-      <c r="AZ162" t="inlineStr">
+      <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/118850750</t>
         </is>
@@ -19607,6 +19709,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 2932-2024 artfynd.xlsx
+++ b/artfynd/S 2932-2024 artfynd.xlsx
@@ -16548,7 +16548,7 @@
         <v>136813846</v>
       </c>
       <c r="B139" t="n">
-        <v>111358</v>
+        <v>111360</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>

--- a/artfynd/S 2932-2024 artfynd.xlsx
+++ b/artfynd/S 2932-2024 artfynd.xlsx
@@ -16548,7 +16548,7 @@
         <v>136813846</v>
       </c>
       <c r="B139" t="n">
-        <v>111360</v>
+        <v>111366</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>

--- a/artfynd/S 2932-2024 artfynd.xlsx
+++ b/artfynd/S 2932-2024 artfynd.xlsx
@@ -6469,7 +6469,7 @@
         <v>137066943</v>
       </c>
       <c r="B52" t="n">
-        <v>91693</v>
+        <v>91694</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -16654,7 +16654,7 @@
         <v>136813846</v>
       </c>
       <c r="B140" t="n">
-        <v>111368</v>
+        <v>111369</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>

--- a/artfynd/S 2932-2024 artfynd.xlsx
+++ b/artfynd/S 2932-2024 artfynd.xlsx
@@ -6469,7 +6469,7 @@
         <v>137066943</v>
       </c>
       <c r="B52" t="n">
-        <v>91694</v>
+        <v>91700</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -16654,7 +16654,7 @@
         <v>136813846</v>
       </c>
       <c r="B140" t="n">
-        <v>111369</v>
+        <v>111375</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>

--- a/artfynd/S 2932-2024 artfynd.xlsx
+++ b/artfynd/S 2932-2024 artfynd.xlsx
@@ -6469,7 +6469,7 @@
         <v>137066943</v>
       </c>
       <c r="B52" t="n">
-        <v>91700</v>
+        <v>91704</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -16654,7 +16654,7 @@
         <v>136813846</v>
       </c>
       <c r="B140" t="n">
-        <v>111375</v>
+        <v>111379</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>

--- a/artfynd/S 2932-2024 artfynd.xlsx
+++ b/artfynd/S 2932-2024 artfynd.xlsx
@@ -6469,7 +6469,7 @@
         <v>137066943</v>
       </c>
       <c r="B52" t="n">
-        <v>91724</v>
+        <v>91734</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -16654,7 +16654,7 @@
         <v>136813846</v>
       </c>
       <c r="B140" t="n">
-        <v>111404</v>
+        <v>111426</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>

--- a/artfynd/S 2932-2024 artfynd.xlsx
+++ b/artfynd/S 2932-2024 artfynd.xlsx
@@ -6469,7 +6469,7 @@
         <v>137066943</v>
       </c>
       <c r="B52" t="n">
-        <v>91734</v>
+        <v>91735</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -16654,7 +16654,7 @@
         <v>136813846</v>
       </c>
       <c r="B140" t="n">
-        <v>111426</v>
+        <v>111427</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>

--- a/artfynd/S 2932-2024 artfynd.xlsx
+++ b/artfynd/S 2932-2024 artfynd.xlsx
@@ -6469,7 +6469,7 @@
         <v>137066943</v>
       </c>
       <c r="B52" t="n">
-        <v>91735</v>
+        <v>91738</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -16654,7 +16654,7 @@
         <v>136813846</v>
       </c>
       <c r="B140" t="n">
-        <v>111427</v>
+        <v>111432</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>

--- a/artfynd/S 2932-2024 artfynd.xlsx
+++ b/artfynd/S 2932-2024 artfynd.xlsx
@@ -6469,7 +6469,7 @@
         <v>137066943</v>
       </c>
       <c r="B52" t="n">
-        <v>91738</v>
+        <v>91740</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -16654,7 +16654,7 @@
         <v>136813846</v>
       </c>
       <c r="B140" t="n">
-        <v>111432</v>
+        <v>111435</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>

--- a/artfynd/S 2932-2024 artfynd.xlsx
+++ b/artfynd/S 2932-2024 artfynd.xlsx
@@ -6469,7 +6469,7 @@
         <v>137066943</v>
       </c>
       <c r="B52" t="n">
-        <v>91740</v>
+        <v>91745</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -16654,7 +16654,7 @@
         <v>136813846</v>
       </c>
       <c r="B140" t="n">
-        <v>111435</v>
+        <v>111441</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>

--- a/artfynd/S 2932-2024 artfynd.xlsx
+++ b/artfynd/S 2932-2024 artfynd.xlsx
@@ -16654,7 +16654,7 @@
         <v>136813846</v>
       </c>
       <c r="B140" t="n">
-        <v>111441</v>
+        <v>111442</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>

--- a/artfynd/S 2932-2024 artfynd.xlsx
+++ b/artfynd/S 2932-2024 artfynd.xlsx
@@ -6469,7 +6469,7 @@
         <v>137066943</v>
       </c>
       <c r="B52" t="n">
-        <v>91745</v>
+        <v>91757</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/S 2932-2024 artfynd.xlsx
+++ b/artfynd/S 2932-2024 artfynd.xlsx
@@ -6469,7 +6469,7 @@
         <v>137066943</v>
       </c>
       <c r="B52" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/S 2932-2024 artfynd.xlsx
+++ b/artfynd/S 2932-2024 artfynd.xlsx
@@ -6469,7 +6469,7 @@
         <v>137066943</v>
       </c>
       <c r="B52" t="n">
-        <v>91758</v>
+        <v>91761</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/S 2932-2024 artfynd.xlsx
+++ b/artfynd/S 2932-2024 artfynd.xlsx
@@ -6469,7 +6469,7 @@
         <v>137066943</v>
       </c>
       <c r="B52" t="n">
-        <v>91761</v>
+        <v>91765</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
         <v>137518758</v>
       </c>
       <c r="B53" t="n">
-        <v>91762</v>
+        <v>91765</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
